--- a/3 Research Paper Online Appendix/G Segment Profiles/tables/Table_G17_Policy_Typology.xlsx
+++ b/3 Research Paper Online Appendix/G Segment Profiles/tables/Table_G17_Policy_Typology.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="95" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="119" uniqueCount="79">
   <si>
     <t>segment</t>
   </si>
@@ -237,6 +237,21 @@
   </si>
   <si>
     <t>Validation of segment differences across class-defining and external outcomes.</t>
+  </si>
+  <si>
+    <t>3 Research Paper Online Appendix/G Segment Profiles/figures/Figure_G1_Class_Profile_Probabilities.png</t>
+  </si>
+  <si>
+    <t>3 Research Paper Online Appendix/G Segment Profiles/figures/Figure_G2_Standardized_Centroids.png</t>
+  </si>
+  <si>
+    <t>3 Research Paper Online Appendix/G Segment Profiles/figures/Figure_G3_Segment_Sizes.png</t>
+  </si>
+  <si>
+    <t>3 Research Paper Online Appendix/G Segment Profiles/figures/Figure_G5_Posterior_Certainty_by_Segment.png</t>
+  </si>
+  <si>
+    <t>3 Research Paper Online Appendix/G Segment Profiles/figures/Figure_G6_Class_Defining_Outcomes.png</t>
   </si>
 </sst>
 </file>
@@ -752,7 +767,7 @@
         <v>57</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s">
         <v>69</v>
@@ -766,7 +781,7 @@
         <v>58</v>
       </c>
       <c r="C3" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="D3" t="s">
         <v>70</v>
@@ -780,7 +795,7 @@
         <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="D4" t="s">
         <v>71</v>
@@ -794,7 +809,7 @@
         <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="D5" t="s">
         <v>72</v>
@@ -808,7 +823,7 @@
         <v>61</v>
       </c>
       <c r="C6" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="D6" t="s">
         <v>73</v>
